--- a/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Precificação" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>Fator sobre A37</t>
   </si>
@@ -191,6 +192,15 @@
   </si>
   <si>
     <t>Domaine Trapet</t>
+  </si>
+  <si>
+    <t>Markup alvo (após Simples ÷ custo)</t>
+  </si>
+  <si>
+    <t>Preço de venda (custo × 1,4 ÷ 0,92)</t>
+  </si>
+  <si>
+    <t>Markup (conferência)</t>
   </si>
 </sst>
 </file>
@@ -1752,6 +1762,415 @@
   </sheetData>
   <autoFilter ref="A5:J34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="4">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1505.11125</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6*$B$1</f>
+        <v>1700.7757124999998</v>
+      </c>
+      <c r="G6" s="5">
+        <f>F6*$B$2/(1-$B$3)</f>
+        <v>2588.136953804347</v>
+      </c>
+      <c r="H6" s="5">
+        <f>G6*$B$3</f>
+        <v>207.05095630434775</v>
+      </c>
+      <c r="I6" s="5">
+        <f>G6-H6</f>
+        <v>2381.085997499999</v>
+      </c>
+      <c r="J6" s="6">
+        <f>I6/F6</f>
+        <v>1.3999999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="8">
+        <v>3</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1579.4269499999998</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*$B$1</f>
+        <v>1784.7524534999995</v>
+      </c>
+      <c r="G7" s="9">
+        <f>F7*$B$2/(1-$B$3)</f>
+        <v>2715.927646630434</v>
+      </c>
+      <c r="H7" s="9">
+        <f>G7*$B$3</f>
+        <v>217.27421173043473</v>
+      </c>
+      <c r="I7" s="9">
+        <f>G7-H7</f>
+        <v>2498.6534348999994</v>
+      </c>
+      <c r="J7" s="10">
+        <f>I7/F7</f>
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="4">
+        <v>45</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1588.4368499999998</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8*$B$1</f>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="G8" s="5">
+        <f>F8*$B$2/(1-$B$3)</f>
+        <v>2731.420757282608</v>
+      </c>
+      <c r="H8" s="5">
+        <f>G8*$B$3</f>
+        <v>218.51366058260865</v>
+      </c>
+      <c r="I8" s="5">
+        <f>G8-H8</f>
+        <v>2512.9070966999993</v>
+      </c>
+      <c r="J8" s="6">
+        <f>I8/F8</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="8">
+        <v>36</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1588.4368499999998</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9*$B$1</f>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="G9" s="9">
+        <f>F9*$B$2/(1-$B$3)</f>
+        <v>2731.420757282608</v>
+      </c>
+      <c r="H9" s="9">
+        <f>G9*$B$3</f>
+        <v>218.51366058260865</v>
+      </c>
+      <c r="I9" s="9">
+        <f>G9-H9</f>
+        <v>2512.9070966999993</v>
+      </c>
+      <c r="J9" s="10">
+        <f>I9/F9</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1701.8380499999998</v>
+      </c>
+      <c r="F10" s="5">
+        <f>E10*$B$1</f>
+        <v>1923.0769964999997</v>
+      </c>
+      <c r="G10" s="5">
+        <f>F10*$B$2/(1-$B$3)</f>
+        <v>2926.421516413043</v>
+      </c>
+      <c r="H10" s="5">
+        <f>G10*$B$3</f>
+        <v>234.11372131304344</v>
+      </c>
+      <c r="I10" s="5">
+        <f>G10-H10</f>
+        <v>2692.3077950999996</v>
+      </c>
+      <c r="J10" s="6">
+        <f>I10/F10</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="8">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1760.4662999999998</v>
+      </c>
+      <c r="F11" s="9">
+        <f>E11*$B$1</f>
+        <v>1989.3269189999996</v>
+      </c>
+      <c r="G11" s="9">
+        <f>F11*$B$2/(1-$B$3)</f>
+        <v>3027.236615869564</v>
+      </c>
+      <c r="H11" s="9">
+        <f>G11*$B$3</f>
+        <v>242.17892926956512</v>
+      </c>
+      <c r="I11" s="9">
+        <f>G11-H11</f>
+        <v>2785.0576865999988</v>
+      </c>
+      <c r="J11" s="10">
+        <f>I11/F11</f>
+        <v>1.3999999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2002</v>
+      </c>
+      <c r="D12" s="4">
+        <v>39</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1808.5191</v>
+      </c>
+      <c r="F12" s="5">
+        <f>E12*$B$1</f>
+        <v>2043.6265829999998</v>
+      </c>
+      <c r="G12" s="5">
+        <f>F12*$B$2/(1-$B$3)</f>
+        <v>3109.8665393478254</v>
+      </c>
+      <c r="H12" s="5">
+        <f>G12*$B$3</f>
+        <v>248.78932314782605</v>
+      </c>
+      <c r="I12" s="5">
+        <f>G12-H12</f>
+        <v>2861.0772161999994</v>
+      </c>
+      <c r="J12" s="6">
+        <f>I12/F12</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="8">
+        <v>28</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1809.8290499999998</v>
+      </c>
+      <c r="F13" s="9">
+        <f>E13*$B$1</f>
+        <v>2045.1068264999997</v>
+      </c>
+      <c r="G13" s="9">
+        <f>F13*$B$2/(1-$B$3)</f>
+        <v>3112.119083804347</v>
+      </c>
+      <c r="H13" s="9">
+        <f>G13*$B$3</f>
+        <v>248.96952670434777</v>
+      </c>
+      <c r="I13" s="9">
+        <f>G13-H13</f>
+        <v>2863.1495570999996</v>
+      </c>
+      <c r="J13" s="10">
+        <f>I13/F13</f>
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1852.79115</v>
+      </c>
+      <c r="F14" s="5">
+        <f>E14*$B$1</f>
+        <v>2093.6539995</v>
+      </c>
+      <c r="G14" s="5">
+        <f>F14*$B$2/(1-$B$3)</f>
+        <v>3185.9952166304342</v>
+      </c>
+      <c r="H14" s="5">
+        <f>G14*$B$3</f>
+        <v>254.87961733043474</v>
+      </c>
+      <c r="I14" s="5">
+        <f>G14-H14</f>
+        <v>2931.1155992999993</v>
+      </c>
+      <c r="J14" s="6">
+        <f>I14/F14</f>
+        <v>1.3999999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="Precificação" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Markup 1,33" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="64">
   <si>
     <t>Fator sobre A37</t>
   </si>
@@ -201,6 +202,9 @@
   </si>
   <si>
     <t>Markup (conferência)</t>
+  </si>
+  <si>
+    <t>Preço de venda (custo × 1,33 ÷ 0,92)</t>
   </si>
 </sst>
 </file>
@@ -2171,6 +2175,489 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2067.87855</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6*$B$1</f>
+        <v>2336.7027614999997</v>
+      </c>
+      <c r="G6" s="5">
+        <f>F6*$B$2/(1-$B$3)</f>
+        <v>3378.0594269510866</v>
+      </c>
+      <c r="H6" s="5">
+        <f>G6*$B$3</f>
+        <v>270.2447541560869</v>
+      </c>
+      <c r="I6" s="5">
+        <f>G6-H6</f>
+        <v>3107.8146727949998</v>
+      </c>
+      <c r="J6" s="6">
+        <f>I6/F6</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D7" s="8">
+        <v>23</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2120.40435</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*$B$1</f>
+        <v>2396.0569154999994</v>
+      </c>
+      <c r="G7" s="9">
+        <f>F7*$B$2/(1-$B$3)</f>
+        <v>3463.8648887119557</v>
+      </c>
+      <c r="H7" s="9">
+        <f>G7*$B$3</f>
+        <v>277.10919109695647</v>
+      </c>
+      <c r="I7" s="9">
+        <f>G7-H7</f>
+        <v>3186.755697614999</v>
+      </c>
+      <c r="J7" s="10">
+        <f>I7/F7</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="4">
+        <v>52</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2172.46155</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8*$B$1</f>
+        <v>2454.8815514999997</v>
+      </c>
+      <c r="G8" s="5">
+        <f>F8*$B$2/(1-$B$3)</f>
+        <v>3548.9048516249995</v>
+      </c>
+      <c r="H8" s="5">
+        <f>G8*$B$3</f>
+        <v>283.91238812999995</v>
+      </c>
+      <c r="I8" s="5">
+        <f>G8-H8</f>
+        <v>3264.9924634949994</v>
+      </c>
+      <c r="J8" s="6">
+        <f>I8/F8</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2181.68445</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9*$B$1</f>
+        <v>2465.3034285</v>
+      </c>
+      <c r="G9" s="9">
+        <f>F9*$B$2/(1-$B$3)</f>
+        <v>3563.971260766304</v>
+      </c>
+      <c r="H9" s="9">
+        <f>G9*$B$3</f>
+        <v>285.11770086130434</v>
+      </c>
+      <c r="I9" s="9">
+        <f>G9-H9</f>
+        <v>3278.8535599049997</v>
+      </c>
+      <c r="J9" s="10">
+        <f>I9/F9</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2212.54815</v>
+      </c>
+      <c r="F10" s="5">
+        <f>E10*$B$1</f>
+        <v>2500.1794095</v>
+      </c>
+      <c r="G10" s="5">
+        <f>F10*$B$2/(1-$B$3)</f>
+        <v>3614.389798516305</v>
+      </c>
+      <c r="H10" s="5">
+        <f>G10*$B$3</f>
+        <v>289.1511838813044</v>
+      </c>
+      <c r="I10" s="5">
+        <f>G10-H10</f>
+        <v>3325.2386146350004</v>
+      </c>
+      <c r="J10" s="6">
+        <f>I10/F10</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2006</v>
+      </c>
+      <c r="D11" s="8">
+        <v>24</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2373.7785</v>
+      </c>
+      <c r="F11" s="9">
+        <f>E11*$B$1</f>
+        <v>2682.3697049999996</v>
+      </c>
+      <c r="G11" s="9">
+        <f>F11*$B$2/(1-$B$3)</f>
+        <v>3877.7735952717385</v>
+      </c>
+      <c r="H11" s="9">
+        <f>G11*$B$3</f>
+        <v>310.2218876217391</v>
+      </c>
+      <c r="I11" s="9">
+        <f>G11-H11</f>
+        <v>3567.5517076499996</v>
+      </c>
+      <c r="J11" s="10">
+        <f>I11/F11</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2437.90215</v>
+      </c>
+      <c r="F12" s="5">
+        <f>E12*$B$1</f>
+        <v>2754.8294294999996</v>
+      </c>
+      <c r="G12" s="5">
+        <f>F12*$B$2/(1-$B$3)</f>
+        <v>3982.525153516304</v>
+      </c>
+      <c r="H12" s="5">
+        <f>G12*$B$3</f>
+        <v>318.6020122813043</v>
+      </c>
+      <c r="I12" s="5">
+        <f>G12-H12</f>
+        <v>3663.9231412349995</v>
+      </c>
+      <c r="J12" s="6">
+        <f>I12/F12</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="8">
+        <v>3</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2497.7445000000002</v>
+      </c>
+      <c r="F13" s="9">
+        <f>E13*$B$1</f>
+        <v>2822.451285</v>
+      </c>
+      <c r="G13" s="9">
+        <f>F13*$B$2/(1-$B$3)</f>
+        <v>4080.2828359239134</v>
+      </c>
+      <c r="H13" s="9">
+        <f>G13*$B$3</f>
+        <v>326.4226268739131</v>
+      </c>
+      <c r="I13" s="9">
+        <f>G13-H13</f>
+        <v>3753.8602090500003</v>
+      </c>
+      <c r="J13" s="10">
+        <f>I13/F13</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D14" s="4">
+        <v>23</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2683.66155</v>
+      </c>
+      <c r="F14" s="5">
+        <f>E14*$B$1</f>
+        <v>3032.5375514999996</v>
+      </c>
+      <c r="G14" s="5">
+        <f>F14*$B$2/(1-$B$3)</f>
+        <v>4383.994503798913</v>
+      </c>
+      <c r="H14" s="5">
+        <f>G14*$B$3</f>
+        <v>350.71956030391306</v>
+      </c>
+      <c r="I14" s="5">
+        <f>G14-H14</f>
+        <v>4033.2749434949997</v>
+      </c>
+      <c r="J14" s="6">
+        <f>I14/F14</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2909.3244</v>
+      </c>
+      <c r="F15" s="9">
+        <f>E15*$B$1</f>
+        <v>3287.5365719999995</v>
+      </c>
+      <c r="G15" s="9">
+        <f>F15*$B$2/(1-$B$3)</f>
+        <v>4752.634392130433</v>
+      </c>
+      <c r="H15" s="9">
+        <f>G15*$B$3</f>
+        <v>380.21075137043465</v>
+      </c>
+      <c r="I15" s="9">
+        <f>G15-H15</f>
+        <v>4372.423640759998</v>
+      </c>
+      <c r="J15" s="10">
+        <f>I15/F15</f>
+        <v>1.3299999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D16" s="4">
+        <v>33</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3057.1250999999997</v>
+      </c>
+      <c r="F16" s="5">
+        <f>E16*$B$1</f>
+        <v>3454.5513629999996</v>
+      </c>
+      <c r="G16" s="5">
+        <f>F16*$B$2/(1-$B$3)</f>
+        <v>4994.079687815217</v>
+      </c>
+      <c r="H16" s="5">
+        <f>G16*$B$3</f>
+        <v>399.52637502521736</v>
+      </c>
+      <c r="I16" s="5">
+        <f>G16-H16</f>
+        <v>4594.55331279</v>
+      </c>
+      <c r="J16" s="6">
+        <f>I16/F16</f>
+        <v>1.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="Precificação" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Markup 1,33" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Markup 1,25" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
   <si>
     <t>Fator sobre A37</t>
   </si>
@@ -205,6 +206,9 @@
   </si>
   <si>
     <t>Preço de venda (custo × 1,33 ÷ 0,92)</t>
+  </si>
+  <si>
+    <t>Preço de venda (custo × 1,25 ÷ 0,92)</t>
   </si>
 </sst>
 </file>
@@ -2658,6 +2662,267 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="4">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3460.2915</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6*$B$1</f>
+        <v>3910.1293949999995</v>
+      </c>
+      <c r="G6" s="5">
+        <f>F6*$B$2/(1-$B$3)</f>
+        <v>5312.675808423912</v>
+      </c>
+      <c r="H6" s="5">
+        <f>G6*$B$3</f>
+        <v>425.01406467391297</v>
+      </c>
+      <c r="I6" s="5">
+        <f>G6-H6</f>
+        <v>4887.661743749999</v>
+      </c>
+      <c r="J6" s="6">
+        <f>I6/F6</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D7" s="8">
+        <v>4</v>
+      </c>
+      <c r="E7" s="9">
+        <v>3633.5989499999996</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*$B$1</f>
+        <v>4105.966813499999</v>
+      </c>
+      <c r="G7" s="9">
+        <f>F7*$B$2/(1-$B$3)</f>
+        <v>5578.759257472825</v>
+      </c>
+      <c r="H7" s="9">
+        <f>G7*$B$3</f>
+        <v>446.300740597826</v>
+      </c>
+      <c r="I7" s="9">
+        <f>G7-H7</f>
+        <v>5132.458516874999</v>
+      </c>
+      <c r="J7" s="10">
+        <f>I7/F7</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D8" s="4">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3900.4559999999997</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8*$B$1</f>
+        <v>4407.51528</v>
+      </c>
+      <c r="G8" s="5">
+        <f>F8*$B$2/(1-$B$3)</f>
+        <v>5988.471847826087</v>
+      </c>
+      <c r="H8" s="5">
+        <f>G8*$B$3</f>
+        <v>479.0777478260869</v>
+      </c>
+      <c r="I8" s="5">
+        <f>G8-H8</f>
+        <v>5509.3940999999995</v>
+      </c>
+      <c r="J8" s="6">
+        <f>I8/F8</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2020</v>
+      </c>
+      <c r="D9" s="8">
+        <v>14</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4406.89545</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9*$B$1</f>
+        <v>4979.7918585</v>
+      </c>
+      <c r="G9" s="9">
+        <f>F9*$B$2/(1-$B$3)</f>
+        <v>6766.021546874999</v>
+      </c>
+      <c r="H9" s="9">
+        <f>G9*$B$3</f>
+        <v>541.28172375</v>
+      </c>
+      <c r="I9" s="9">
+        <f>G9-H9</f>
+        <v>6224.739823124999</v>
+      </c>
+      <c r="J9" s="10">
+        <f>I9/F9</f>
+        <v>1.2499999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4502.04255</v>
+      </c>
+      <c r="F10" s="5">
+        <f>E10*$B$1</f>
+        <v>5087.308081499999</v>
+      </c>
+      <c r="G10" s="5">
+        <f>F10*$B$2/(1-$B$3)</f>
+        <v>6912.10337160326</v>
+      </c>
+      <c r="H10" s="5">
+        <f>G10*$B$3</f>
+        <v>552.9682697282608</v>
+      </c>
+      <c r="I10" s="5">
+        <f>G10-H10</f>
+        <v>6359.135101874999</v>
+      </c>
+      <c r="J10" s="6">
+        <f>I10/F10</f>
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Markup 1,33" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Markup 1,25" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Markup 1,20" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="66">
   <si>
     <t>Fator sobre A37</t>
   </si>
@@ -209,6 +210,9 @@
   </si>
   <si>
     <t>Preço de venda (custo × 1,25 ÷ 0,92)</t>
+  </si>
+  <si>
+    <t>Preço de venda (custo × 1,20 ÷ 0,92)</t>
   </si>
 </sst>
 </file>
@@ -2923,6 +2927,230 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4886.8377</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6*$B$1</f>
+        <v>5522.126601</v>
+      </c>
+      <c r="G6" s="5">
+        <f>F6*$B$2/(1-$B$3)</f>
+        <v>7202.773827391304</v>
+      </c>
+      <c r="H6" s="5">
+        <f>G6*$B$3</f>
+        <v>576.2219061913044</v>
+      </c>
+      <c r="I6" s="5">
+        <f>G6-H6</f>
+        <v>6626.551921199999</v>
+      </c>
+      <c r="J6" s="6">
+        <f>I6/F6</f>
+        <v>1.1999999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="8">
+        <v>25</v>
+      </c>
+      <c r="E7" s="9">
+        <v>6398.3922</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*$B$1</f>
+        <v>7230.183185999999</v>
+      </c>
+      <c r="G7" s="9">
+        <f>F7*$B$2/(1-$B$3)</f>
+        <v>9430.673720869563</v>
+      </c>
+      <c r="H7" s="9">
+        <f>G7*$B$3</f>
+        <v>754.4538976695651</v>
+      </c>
+      <c r="I7" s="9">
+        <f>G7-H7</f>
+        <v>8676.219823199997</v>
+      </c>
+      <c r="J7" s="10">
+        <f>I7/F7</f>
+        <v>1.1999999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2006</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>7386.0518999999995</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8*$B$1</f>
+        <v>8346.238646999998</v>
+      </c>
+      <c r="G8" s="5">
+        <f>F8*$B$2/(1-$B$3)</f>
+        <v>10886.39823521739</v>
+      </c>
+      <c r="H8" s="5">
+        <f>G8*$B$3</f>
+        <v>870.9118588173912</v>
+      </c>
+      <c r="I8" s="5">
+        <f>G8-H8</f>
+        <v>10015.486376399998</v>
+      </c>
+      <c r="J8" s="6">
+        <f>I8/F8</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D9" s="8">
+        <v>17</v>
+      </c>
+      <c r="E9" s="9">
+        <v>7479.5269499999995</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9*$B$1</f>
+        <v>8451.865453499999</v>
+      </c>
+      <c r="G9" s="9">
+        <f>F9*$B$2/(1-$B$3)</f>
+        <v>11024.17233065217</v>
+      </c>
+      <c r="H9" s="9">
+        <f>G9*$B$3</f>
+        <v>881.9337864521736</v>
+      </c>
+      <c r="I9" s="9">
+        <f>G9-H9</f>
+        <v>10142.238544199998</v>
+      </c>
+      <c r="J9" s="10">
+        <f>I9/F9</f>
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
+++ b/analises/2026-09-23-tanyno-site-tintos-chardonnay-precificacao.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Precificação" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Markup 1,33" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Markup 1,25" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Markup 1,20" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Preço final" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Markup 1,4" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Markup 1,33" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="Markup 1,25" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Markup 1,20" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="69">
   <si>
     <t>Fator sobre A37</t>
   </si>
@@ -195,6 +196,15 @@
   </si>
   <si>
     <t>Domaine Trapet</t>
+  </si>
+  <si>
+    <t>Preço de venda = custo × markup ÷ (1 − Simples)</t>
+  </si>
+  <si>
+    <t>Preço de venda</t>
+  </si>
+  <si>
+    <t>Conferência (após Simples ÷ custo)</t>
   </si>
   <si>
     <t>Markup alvo (após Simples ÷ custo)</t>
@@ -269,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -291,6 +301,14 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1802,7 +1820,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1.4</v>
@@ -1836,7 +1854,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>10</v>
@@ -1845,7 +1863,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2211,7 +2229,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1.33</v>
@@ -2245,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>10</v>
@@ -2254,7 +2272,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2694,7 +2712,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1.25</v>
@@ -2728,7 +2746,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>10</v>
@@ -2737,7 +2755,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2955,7 +2973,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>1.2</v>
@@ -2989,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>10</v>
@@ -2998,7 +3016,7 @@
         <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3150,6 +3168,1243 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="4">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1505.11125</v>
+      </c>
+      <c r="F6" s="5">
+        <f>E6*$B$1</f>
+        <v>1700.7757124999998</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="12">
+        <f>F6*G6/(1-$B$2)</f>
+        <v>2588.136953804347</v>
+      </c>
+      <c r="I6" s="5">
+        <f>H6*$B$2</f>
+        <v>207.05095630434775</v>
+      </c>
+      <c r="J6" s="5">
+        <f>H6-I6</f>
+        <v>2381.085997499999</v>
+      </c>
+      <c r="K6" s="6">
+        <f>J6/F6</f>
+        <v>1.3999999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="8">
+        <v>3</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1579.4269499999998</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7*$B$1</f>
+        <v>1784.7524534999995</v>
+      </c>
+      <c r="G7" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H7" s="14">
+        <f>F7*G7/(1-$B$2)</f>
+        <v>2715.927646630434</v>
+      </c>
+      <c r="I7" s="9">
+        <f>H7*$B$2</f>
+        <v>217.27421173043473</v>
+      </c>
+      <c r="J7" s="9">
+        <f>H7-I7</f>
+        <v>2498.6534348999994</v>
+      </c>
+      <c r="K7" s="10">
+        <f>J7/F7</f>
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="4">
+        <v>45</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1588.4368499999998</v>
+      </c>
+      <c r="F8" s="5">
+        <f>E8*$B$1</f>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="G8" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H8" s="12">
+        <f>F8*G8/(1-$B$2)</f>
+        <v>2731.420757282608</v>
+      </c>
+      <c r="I8" s="5">
+        <f>H8*$B$2</f>
+        <v>218.51366058260865</v>
+      </c>
+      <c r="J8" s="5">
+        <f>H8-I8</f>
+        <v>2512.9070966999993</v>
+      </c>
+      <c r="K8" s="6">
+        <f>J8/F8</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="8">
+        <v>36</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1588.4368499999998</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9*$B$1</f>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H9" s="14">
+        <f>F9*G9/(1-$B$2)</f>
+        <v>2731.420757282608</v>
+      </c>
+      <c r="I9" s="9">
+        <f>H9*$B$2</f>
+        <v>218.51366058260865</v>
+      </c>
+      <c r="J9" s="9">
+        <f>H9-I9</f>
+        <v>2512.9070966999993</v>
+      </c>
+      <c r="K9" s="10">
+        <f>J9/F9</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1701.8380499999998</v>
+      </c>
+      <c r="F10" s="5">
+        <f>E10*$B$1</f>
+        <v>1923.0769964999997</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="12">
+        <f>F10*G10/(1-$B$2)</f>
+        <v>2926.421516413043</v>
+      </c>
+      <c r="I10" s="5">
+        <f>H10*$B$2</f>
+        <v>234.11372131304344</v>
+      </c>
+      <c r="J10" s="5">
+        <f>H10-I10</f>
+        <v>2692.3077950999996</v>
+      </c>
+      <c r="K10" s="6">
+        <f>J10/F10</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="8">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1760.4662999999998</v>
+      </c>
+      <c r="F11" s="9">
+        <f>E11*$B$1</f>
+        <v>1989.3269189999996</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H11" s="14">
+        <f>F11*G11/(1-$B$2)</f>
+        <v>3027.236615869564</v>
+      </c>
+      <c r="I11" s="9">
+        <f>H11*$B$2</f>
+        <v>242.17892926956512</v>
+      </c>
+      <c r="J11" s="9">
+        <f>H11-I11</f>
+        <v>2785.0576865999988</v>
+      </c>
+      <c r="K11" s="10">
+        <f>J11/F11</f>
+        <v>1.3999999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2002</v>
+      </c>
+      <c r="D12" s="4">
+        <v>39</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1808.5191</v>
+      </c>
+      <c r="F12" s="5">
+        <f>E12*$B$1</f>
+        <v>2043.6265829999998</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H12" s="12">
+        <f>F12*G12/(1-$B$2)</f>
+        <v>3109.8665393478254</v>
+      </c>
+      <c r="I12" s="5">
+        <f>H12*$B$2</f>
+        <v>248.78932314782605</v>
+      </c>
+      <c r="J12" s="5">
+        <f>H12-I12</f>
+        <v>2861.0772161999994</v>
+      </c>
+      <c r="K12" s="6">
+        <f>J12/F12</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D13" s="8">
+        <v>28</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1809.8290499999998</v>
+      </c>
+      <c r="F13" s="9">
+        <f>E13*$B$1</f>
+        <v>2045.1068264999997</v>
+      </c>
+      <c r="G13" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H13" s="14">
+        <f>F13*G13/(1-$B$2)</f>
+        <v>3112.119083804347</v>
+      </c>
+      <c r="I13" s="9">
+        <f>H13*$B$2</f>
+        <v>248.96952670434777</v>
+      </c>
+      <c r="J13" s="9">
+        <f>H13-I13</f>
+        <v>2863.1495570999996</v>
+      </c>
+      <c r="K13" s="10">
+        <f>J13/F13</f>
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1852.79115</v>
+      </c>
+      <c r="F14" s="5">
+        <f>E14*$B$1</f>
+        <v>2093.6539995</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1.4</v>
+      </c>
+      <c r="H14" s="12">
+        <f>F14*G14/(1-$B$2)</f>
+        <v>3185.9952166304342</v>
+      </c>
+      <c r="I14" s="5">
+        <f>H14*$B$2</f>
+        <v>254.87961733043474</v>
+      </c>
+      <c r="J14" s="5">
+        <f>H14-I14</f>
+        <v>2931.1155992999993</v>
+      </c>
+      <c r="K14" s="6">
+        <f>J14/F14</f>
+        <v>1.3999999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="8">
+        <v>5</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2067.87855</v>
+      </c>
+      <c r="F15" s="9">
+        <f>E15*$B$1</f>
+        <v>2336.7027614999997</v>
+      </c>
+      <c r="G15" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H15" s="14">
+        <f>F15*G15/(1-$B$2)</f>
+        <v>3378.0594269510866</v>
+      </c>
+      <c r="I15" s="9">
+        <f>H15*$B$2</f>
+        <v>270.2447541560869</v>
+      </c>
+      <c r="J15" s="9">
+        <f>H15-I15</f>
+        <v>3107.8146727949998</v>
+      </c>
+      <c r="K15" s="10">
+        <f>J15/F15</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D16" s="4">
+        <v>23</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2120.40435</v>
+      </c>
+      <c r="F16" s="5">
+        <f>E16*$B$1</f>
+        <v>2396.0569154999994</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="H16" s="12">
+        <f>F16*G16/(1-$B$2)</f>
+        <v>3463.8648887119557</v>
+      </c>
+      <c r="I16" s="5">
+        <f>H16*$B$2</f>
+        <v>277.10919109695647</v>
+      </c>
+      <c r="J16" s="5">
+        <f>H16-I16</f>
+        <v>3186.755697614999</v>
+      </c>
+      <c r="K16" s="6">
+        <f>J16/F16</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D17" s="8">
+        <v>52</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2172.46155</v>
+      </c>
+      <c r="F17" s="9">
+        <f>E17*$B$1</f>
+        <v>2454.8815514999997</v>
+      </c>
+      <c r="G17" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H17" s="14">
+        <f>F17*G17/(1-$B$2)</f>
+        <v>3548.9048516249995</v>
+      </c>
+      <c r="I17" s="9">
+        <f>H17*$B$2</f>
+        <v>283.91238812999995</v>
+      </c>
+      <c r="J17" s="9">
+        <f>H17-I17</f>
+        <v>3264.9924634949994</v>
+      </c>
+      <c r="K17" s="10">
+        <f>J17/F17</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2181.68445</v>
+      </c>
+      <c r="F18" s="5">
+        <f>E18*$B$1</f>
+        <v>2465.3034285</v>
+      </c>
+      <c r="G18" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="H18" s="12">
+        <f>F18*G18/(1-$B$2)</f>
+        <v>3563.971260766304</v>
+      </c>
+      <c r="I18" s="5">
+        <f>H18*$B$2</f>
+        <v>285.11770086130434</v>
+      </c>
+      <c r="J18" s="5">
+        <f>H18-I18</f>
+        <v>3278.8535599049997</v>
+      </c>
+      <c r="K18" s="6">
+        <f>J18/F18</f>
+        <v>1.3299999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2212.54815</v>
+      </c>
+      <c r="F19" s="9">
+        <f>E19*$B$1</f>
+        <v>2500.1794095</v>
+      </c>
+      <c r="G19" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H19" s="14">
+        <f>F19*G19/(1-$B$2)</f>
+        <v>3614.389798516305</v>
+      </c>
+      <c r="I19" s="9">
+        <f>H19*$B$2</f>
+        <v>289.1511838813044</v>
+      </c>
+      <c r="J19" s="9">
+        <f>H19-I19</f>
+        <v>3325.2386146350004</v>
+      </c>
+      <c r="K19" s="10">
+        <f>J19/F19</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2006</v>
+      </c>
+      <c r="D20" s="4">
+        <v>24</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2373.7785</v>
+      </c>
+      <c r="F20" s="5">
+        <f>E20*$B$1</f>
+        <v>2682.3697049999996</v>
+      </c>
+      <c r="G20" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="H20" s="12">
+        <f>F20*G20/(1-$B$2)</f>
+        <v>3877.7735952717385</v>
+      </c>
+      <c r="I20" s="5">
+        <f>H20*$B$2</f>
+        <v>310.2218876217391</v>
+      </c>
+      <c r="J20" s="5">
+        <f>H20-I20</f>
+        <v>3567.5517076499996</v>
+      </c>
+      <c r="K20" s="6">
+        <f>J20/F20</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2016</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2437.90215</v>
+      </c>
+      <c r="F21" s="9">
+        <f>E21*$B$1</f>
+        <v>2754.8294294999996</v>
+      </c>
+      <c r="G21" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H21" s="14">
+        <f>F21*G21/(1-$B$2)</f>
+        <v>3982.525153516304</v>
+      </c>
+      <c r="I21" s="9">
+        <f>H21*$B$2</f>
+        <v>318.6020122813043</v>
+      </c>
+      <c r="J21" s="9">
+        <f>H21-I21</f>
+        <v>3663.9231412349995</v>
+      </c>
+      <c r="K21" s="10">
+        <f>J21/F21</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D22" s="4">
+        <v>3</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2497.7445000000002</v>
+      </c>
+      <c r="F22" s="5">
+        <f>E22*$B$1</f>
+        <v>2822.451285</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="H22" s="12">
+        <f>F22*G22/(1-$B$2)</f>
+        <v>4080.2828359239134</v>
+      </c>
+      <c r="I22" s="5">
+        <f>H22*$B$2</f>
+        <v>326.4226268739131</v>
+      </c>
+      <c r="J22" s="5">
+        <f>H22-I22</f>
+        <v>3753.8602090500003</v>
+      </c>
+      <c r="K22" s="6">
+        <f>J22/F22</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D23" s="8">
+        <v>23</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2683.66155</v>
+      </c>
+      <c r="F23" s="9">
+        <f>E23*$B$1</f>
+        <v>3032.5375514999996</v>
+      </c>
+      <c r="G23" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H23" s="14">
+        <f>F23*G23/(1-$B$2)</f>
+        <v>4383.994503798913</v>
+      </c>
+      <c r="I23" s="9">
+        <f>H23*$B$2</f>
+        <v>350.71956030391306</v>
+      </c>
+      <c r="J23" s="9">
+        <f>H23-I23</f>
+        <v>4033.2749434949997</v>
+      </c>
+      <c r="K23" s="10">
+        <f>J23/F23</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2909.3244</v>
+      </c>
+      <c r="F24" s="5">
+        <f>E24*$B$1</f>
+        <v>3287.5365719999995</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1.33</v>
+      </c>
+      <c r="H24" s="12">
+        <f>F24*G24/(1-$B$2)</f>
+        <v>4752.634392130433</v>
+      </c>
+      <c r="I24" s="5">
+        <f>H24*$B$2</f>
+        <v>380.21075137043465</v>
+      </c>
+      <c r="J24" s="5">
+        <f>H24-I24</f>
+        <v>4372.423640759998</v>
+      </c>
+      <c r="K24" s="6">
+        <f>J24/F24</f>
+        <v>1.3299999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="8">
+        <v>33</v>
+      </c>
+      <c r="E25" s="9">
+        <v>3057.1250999999997</v>
+      </c>
+      <c r="F25" s="9">
+        <f>E25*$B$1</f>
+        <v>3454.5513629999996</v>
+      </c>
+      <c r="G25" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="H25" s="14">
+        <f>F25*G25/(1-$B$2)</f>
+        <v>4994.079687815217</v>
+      </c>
+      <c r="I25" s="9">
+        <f>H25*$B$2</f>
+        <v>399.52637502521736</v>
+      </c>
+      <c r="J25" s="9">
+        <f>H25-I25</f>
+        <v>4594.55331279</v>
+      </c>
+      <c r="K25" s="10">
+        <f>J25/F25</f>
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D26" s="4">
+        <v>13</v>
+      </c>
+      <c r="E26" s="5">
+        <v>3460.2915</v>
+      </c>
+      <c r="F26" s="5">
+        <f>E26*$B$1</f>
+        <v>3910.1293949999995</v>
+      </c>
+      <c r="G26" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="H26" s="12">
+        <f>F26*G26/(1-$B$2)</f>
+        <v>5312.675808423912</v>
+      </c>
+      <c r="I26" s="5">
+        <f>H26*$B$2</f>
+        <v>425.01406467391297</v>
+      </c>
+      <c r="J26" s="5">
+        <f>H26-I26</f>
+        <v>4887.661743749999</v>
+      </c>
+      <c r="K26" s="6">
+        <f>J26/F26</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2022</v>
+      </c>
+      <c r="D27" s="8">
+        <v>4</v>
+      </c>
+      <c r="E27" s="9">
+        <v>3633.5989499999996</v>
+      </c>
+      <c r="F27" s="9">
+        <f>E27*$B$1</f>
+        <v>4105.966813499999</v>
+      </c>
+      <c r="G27" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="H27" s="14">
+        <f>F27*G27/(1-$B$2)</f>
+        <v>5578.759257472825</v>
+      </c>
+      <c r="I27" s="9">
+        <f>H27*$B$2</f>
+        <v>446.300740597826</v>
+      </c>
+      <c r="J27" s="9">
+        <f>H27-I27</f>
+        <v>5132.458516874999</v>
+      </c>
+      <c r="K27" s="10">
+        <f>J27/F27</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D28" s="4">
+        <v>16</v>
+      </c>
+      <c r="E28" s="5">
+        <v>3900.4559999999997</v>
+      </c>
+      <c r="F28" s="5">
+        <f>E28*$B$1</f>
+        <v>4407.51528</v>
+      </c>
+      <c r="G28" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="H28" s="12">
+        <f>F28*G28/(1-$B$2)</f>
+        <v>5988.471847826087</v>
+      </c>
+      <c r="I28" s="5">
+        <f>H28*$B$2</f>
+        <v>479.0777478260869</v>
+      </c>
+      <c r="J28" s="5">
+        <f>H28-I28</f>
+        <v>5509.3940999999995</v>
+      </c>
+      <c r="K28" s="6">
+        <f>J28/F28</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2020</v>
+      </c>
+      <c r="D29" s="8">
+        <v>14</v>
+      </c>
+      <c r="E29" s="9">
+        <v>4406.89545</v>
+      </c>
+      <c r="F29" s="9">
+        <f>E29*$B$1</f>
+        <v>4979.7918585</v>
+      </c>
+      <c r="G29" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="H29" s="14">
+        <f>F29*G29/(1-$B$2)</f>
+        <v>6766.021546874999</v>
+      </c>
+      <c r="I29" s="9">
+        <f>H29*$B$2</f>
+        <v>541.28172375</v>
+      </c>
+      <c r="J29" s="9">
+        <f>H29-I29</f>
+        <v>6224.739823124999</v>
+      </c>
+      <c r="K29" s="10">
+        <f>J29/F29</f>
+        <v>1.2499999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5">
+        <v>4502.04255</v>
+      </c>
+      <c r="F30" s="5">
+        <f>E30*$B$1</f>
+        <v>5087.308081499999</v>
+      </c>
+      <c r="G30" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="H30" s="12">
+        <f>F30*G30/(1-$B$2)</f>
+        <v>6912.10337160326</v>
+      </c>
+      <c r="I30" s="5">
+        <f>H30*$B$2</f>
+        <v>552.9682697282608</v>
+      </c>
+      <c r="J30" s="5">
+        <f>H30-I30</f>
+        <v>6359.135101874999</v>
+      </c>
+      <c r="K30" s="6">
+        <f>J30/F30</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D31" s="8">
+        <v>22</v>
+      </c>
+      <c r="E31" s="9">
+        <v>4886.8377</v>
+      </c>
+      <c r="F31" s="9">
+        <f>E31*$B$1</f>
+        <v>5522.126601</v>
+      </c>
+      <c r="G31" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="14">
+        <f>F31*G31/(1-$B$2)</f>
+        <v>7202.773827391304</v>
+      </c>
+      <c r="I31" s="9">
+        <f>H31*$B$2</f>
+        <v>576.2219061913044</v>
+      </c>
+      <c r="J31" s="9">
+        <f>H31-I31</f>
+        <v>6626.551921199999</v>
+      </c>
+      <c r="K31" s="10">
+        <f>J31/F31</f>
+        <v>1.1999999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D32" s="4">
+        <v>25</v>
+      </c>
+      <c r="E32" s="5">
+        <v>6398.3922</v>
+      </c>
+      <c r="F32" s="5">
+        <f>E32*$B$1</f>
+        <v>7230.183185999999</v>
+      </c>
+      <c r="G32" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="H32" s="12">
+        <f>F32*G32/(1-$B$2)</f>
+        <v>9430.673720869563</v>
+      </c>
+      <c r="I32" s="5">
+        <f>H32*$B$2</f>
+        <v>754.4538976695651</v>
+      </c>
+      <c r="J32" s="5">
+        <f>H32-I32</f>
+        <v>8676.219823199997</v>
+      </c>
+      <c r="K32" s="6">
+        <f>J32/F32</f>
+        <v>1.1999999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2006</v>
+      </c>
+      <c r="D33" s="8">
+        <v>2</v>
+      </c>
+      <c r="E33" s="9">
+        <v>7386.0518999999995</v>
+      </c>
+      <c r="F33" s="9">
+        <f>E33*$B$1</f>
+        <v>8346.238646999998</v>
+      </c>
+      <c r="G33" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="H33" s="14">
+        <f>F33*G33/(1-$B$2)</f>
+        <v>10886.39823521739</v>
+      </c>
+      <c r="I33" s="9">
+        <f>H33*$B$2</f>
+        <v>870.9118588173912</v>
+      </c>
+      <c r="J33" s="9">
+        <f>H33-I33</f>
+        <v>10015.486376399998</v>
+      </c>
+      <c r="K33" s="10">
+        <f>J33/F33</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D34" s="4">
+        <v>17</v>
+      </c>
+      <c r="E34" s="5">
+        <v>7479.5269499999995</v>
+      </c>
+      <c r="F34" s="5">
+        <f>E34*$B$1</f>
+        <v>8451.865453499999</v>
+      </c>
+      <c r="G34" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="H34" s="12">
+        <f>F34*G34/(1-$B$2)</f>
+        <v>11024.17233065217</v>
+      </c>
+      <c r="I34" s="5">
+        <f>H34*$B$2</f>
+        <v>881.9337864521736</v>
+      </c>
+      <c r="J34" s="5">
+        <f>H34-I34</f>
+        <v>10142.238544199998</v>
+      </c>
+      <c r="K34" s="6">
+        <f>J34/F34</f>
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:K34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
